--- a/branches/migration/2026.0.3-template-v0.11.1/CodeSystem-mii-cs-onko-operation-urgency.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/CodeSystem-mii-cs-onko-operation-urgency.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T10:41:09+00:00</t>
+    <t>2026-08-27T11:11:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/CodeSystem-mii-cs-onko-operation-urgency.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/CodeSystem-mii-cs-onko-operation-urgency.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T11:11:54+00:00</t>
+    <t>2026-08-27T11:29:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/CodeSystem-mii-cs-onko-operation-urgency.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/CodeSystem-mii-cs-onko-operation-urgency.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T11:29:36+00:00</t>
+    <t>2026-08-27T12:06:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/CodeSystem-mii-cs-onko-operation-urgency.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/CodeSystem-mii-cs-onko-operation-urgency.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T12:06:00+00:00</t>
+    <t>2026-08-27T15:31:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/CodeSystem-mii-cs-onko-operation-urgency.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/CodeSystem-mii-cs-onko-operation-urgency.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T15:31:43+00:00</t>
+    <t>2026-08-27T15:57:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/CodeSystem-mii-cs-onko-operation-urgency.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/CodeSystem-mii-cs-onko-operation-urgency.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T15:57:15+00:00</t>
+    <t>2026-08-28T06:12:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/CodeSystem-mii-cs-onko-operation-urgency.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/CodeSystem-mii-cs-onko-operation-urgency.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T06:12:02+00:00</t>
+    <t>2026-08-28T06:31:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/CodeSystem-mii-cs-onko-operation-urgency.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/CodeSystem-mii-cs-onko-operation-urgency.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T06:31:49+00:00</t>
+    <t>2026-08-28T06:49:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/CodeSystem-mii-cs-onko-operation-urgency.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/CodeSystem-mii-cs-onko-operation-urgency.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T06:49:57+00:00</t>
+    <t>2026-08-28T07:24:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/CodeSystem-mii-cs-onko-operation-urgency.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/CodeSystem-mii-cs-onko-operation-urgency.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T07:24:31+00:00</t>
+    <t>2026-08-28T07:40:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/CodeSystem-mii-cs-onko-operation-urgency.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/CodeSystem-mii-cs-onko-operation-urgency.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T07:40:52+00:00</t>
+    <t>2026-08-28T08:03:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/CodeSystem-mii-cs-onko-operation-urgency.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/CodeSystem-mii-cs-onko-operation-urgency.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T08:03:44+00:00</t>
+    <t>2026-08-28T09:05:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/CodeSystem-mii-cs-onko-operation-urgency.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/CodeSystem-mii-cs-onko-operation-urgency.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T09:05:47+00:00</t>
+    <t>2026-08-28T09:25:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/CodeSystem-mii-cs-onko-operation-urgency.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/CodeSystem-mii-cs-onko-operation-urgency.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T09:25:31+00:00</t>
+    <t>2026-08-28T09:53:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/CodeSystem-mii-cs-onko-operation-urgency.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/CodeSystem-mii-cs-onko-operation-urgency.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T09:53:30+00:00</t>
+    <t>2026-08-28T10:16:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/CodeSystem-mii-cs-onko-operation-urgency.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/CodeSystem-mii-cs-onko-operation-urgency.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T10:16:47+00:00</t>
+    <t>2026-08-28T12:10:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/CodeSystem-mii-cs-onko-operation-urgency.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/CodeSystem-mii-cs-onko-operation-urgency.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T12:10:16+00:00</t>
+    <t>2026-08-28T12:26:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/CodeSystem-mii-cs-onko-operation-urgency.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/CodeSystem-mii-cs-onko-operation-urgency.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T12:26:30+00:00</t>
+    <t>2026-08-28T12:47:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/CodeSystem-mii-cs-onko-operation-urgency.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/CodeSystem-mii-cs-onko-operation-urgency.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T12:47:27+00:00</t>
+    <t>2026-08-28T13:10:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/CodeSystem-mii-cs-onko-operation-urgency.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/CodeSystem-mii-cs-onko-operation-urgency.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T13:10:09+00:00</t>
+    <t>2026-08-28T13:33:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/CodeSystem-mii-cs-onko-operation-urgency.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/CodeSystem-mii-cs-onko-operation-urgency.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T13:33:24+00:00</t>
+    <t>2026-08-28T13:57:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/CodeSystem-mii-cs-onko-operation-urgency.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/CodeSystem-mii-cs-onko-operation-urgency.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="52">
   <si>
     <t>Property</t>
   </si>
@@ -54,46 +54,49 @@
     <t>Experimental</t>
   </si>
   <si>
+    <t>false</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>2026-08-28T14:33:40+00:00</t>
+  </si>
+  <si>
+    <t>Publisher</t>
+  </si>
+  <si>
+    <t>Medizininformatik Initiative</t>
+  </si>
+  <si>
+    <t>Contact</t>
+  </si>
+  <si>
+    <t>Medizininformatik Initiative (https://www.medizininformatik-initiative.de/)</t>
+  </si>
+  <si>
+    <t>Jurisdiction</t>
+  </si>
+  <si>
+    <t>Germany</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>oBDS-basiertes Codesystem für die Modalität der Eingriffsdurchführung (Art des Eingriffs KR6)</t>
+  </si>
+  <si>
+    <t>Purpose</t>
+  </si>
+  <si>
+    <t>Copyright</t>
+  </si>
+  <si>
+    <t>Case Sensitive</t>
+  </si>
+  <si>
     <t>true</t>
-  </si>
-  <si>
-    <t>Date</t>
-  </si>
-  <si>
-    <t>2026-08-28T13:57:18+00:00</t>
-  </si>
-  <si>
-    <t>Publisher</t>
-  </si>
-  <si>
-    <t>Medizininformatik Initiative</t>
-  </si>
-  <si>
-    <t>Contact</t>
-  </si>
-  <si>
-    <t>Medizininformatik Initiative (https://www.medizininformatik-initiative.de/)</t>
-  </si>
-  <si>
-    <t>Jurisdiction</t>
-  </si>
-  <si>
-    <t>Germany</t>
-  </si>
-  <si>
-    <t>Description</t>
-  </si>
-  <si>
-    <t>oBDS-basiertes Codesystem für die Modalität der Eingriffsdurchführung (Art des Eingriffs KR6)</t>
-  </si>
-  <si>
-    <t>Purpose</t>
-  </si>
-  <si>
-    <t>Copyright</t>
-  </si>
-  <si>
-    <t>Case Sensitive</t>
   </si>
   <si>
     <t>Value Set (all codes)</t>
@@ -419,55 +422,55 @@
         <v>26</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>13</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B17" s="2"/>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B18" s="2"/>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B19" s="2"/>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B21" s="2"/>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -482,58 +485,58 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D1" t="s" s="1">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C3" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C4" t="s" s="2">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>

--- a/branches/migration/2026.0.3-template-v0.11.1/CodeSystem-mii-cs-onko-operation-urgency.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/CodeSystem-mii-cs-onko-operation-urgency.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T14:33:40+00:00</t>
+    <t>2026-08-28T14:57:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/CodeSystem-mii-cs-onko-operation-urgency.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/CodeSystem-mii-cs-onko-operation-urgency.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T14:57:41+00:00</t>
+    <t>2026-08-28T15:24:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/CodeSystem-mii-cs-onko-operation-urgency.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/CodeSystem-mii-cs-onko-operation-urgency.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T15:24:04+00:00</t>
+    <t>2026-08-28T15:48:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/CodeSystem-mii-cs-onko-operation-urgency.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/CodeSystem-mii-cs-onko-operation-urgency.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T15:48:09+00:00</t>
+    <t>2026-08-28T18:25:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/CodeSystem-mii-cs-onko-operation-urgency.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/CodeSystem-mii-cs-onko-operation-urgency.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T18:25:22+00:00</t>
+    <t>2026-08-28T19:18:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/CodeSystem-mii-cs-onko-operation-urgency.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/CodeSystem-mii-cs-onko-operation-urgency.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T19:18:26+00:00</t>
+    <t>2026-08-31T13:44:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/CodeSystem-mii-cs-onko-operation-urgency.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/CodeSystem-mii-cs-onko-operation-urgency.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T13:44:47+00:00</t>
+    <t>2026-08-31T14:28:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/CodeSystem-mii-cs-onko-operation-urgency.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/CodeSystem-mii-cs-onko-operation-urgency.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T14:28:40+00:00</t>
+    <t>2026-08-31T15:22:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/CodeSystem-mii-cs-onko-operation-urgency.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/CodeSystem-mii-cs-onko-operation-urgency.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T15:22:09+00:00</t>
+    <t>2026-09-01T08:53:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/CodeSystem-mii-cs-onko-operation-urgency.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/CodeSystem-mii-cs-onko-operation-urgency.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T08:53:35+00:00</t>
+    <t>2026-09-01T09:38:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/CodeSystem-mii-cs-onko-operation-urgency.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/CodeSystem-mii-cs-onko-operation-urgency.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T09:38:31+00:00</t>
+    <t>2026-09-01T11:08:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/CodeSystem-mii-cs-onko-operation-urgency.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/CodeSystem-mii-cs-onko-operation-urgency.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T11:08:21+00:00</t>
+    <t>2026-09-01T14:29:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/CodeSystem-mii-cs-onko-operation-urgency.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/CodeSystem-mii-cs-onko-operation-urgency.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T14:29:01+00:00</t>
+    <t>2026-09-01T19:43:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/CodeSystem-mii-cs-onko-operation-urgency.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/CodeSystem-mii-cs-onko-operation-urgency.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T19:43:49+00:00</t>
+    <t>2026-09-01T20:38:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/CodeSystem-mii-cs-onko-operation-urgency.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/CodeSystem-mii-cs-onko-operation-urgency.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T20:38:11+00:00</t>
+    <t>2026-09-01T21:24:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/CodeSystem-mii-cs-onko-operation-urgency.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/CodeSystem-mii-cs-onko-operation-urgency.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T21:24:42+00:00</t>
+    <t>2026-09-01T22:10:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
